--- a/metadata/FWD Data Dictionary.xlsx
+++ b/metadata/FWD Data Dictionary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://opm365-my.sharepoint.com/personal/andrea_brown_opm_gov/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C03867CF-C1FB-4D72-99A3-33FFD51B5C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEE7C909-A67C-4A7F-A9CC-98F7A780EF4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8C197413-4935-4A6B-AEDF-3AC427E4EF9D}"/>
+    <workbookView xWindow="30855" yWindow="1800" windowWidth="21600" windowHeight="11295" xr2:uid="{8C197413-4935-4A6B-AEDF-3AC427E4EF9D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="201">
   <si>
     <t>Field Name</t>
   </si>
@@ -47,15 +47,6 @@
     <t>Sample Value</t>
   </si>
   <si>
-    <t>Employment?</t>
-  </si>
-  <si>
-    <t>Accessions?</t>
-  </si>
-  <si>
-    <t>Separations?</t>
-  </si>
-  <si>
     <t>accession_category</t>
   </si>
   <si>
@@ -603,6 +594,51 @@
   </si>
   <si>
     <t>F</t>
+  </si>
+  <si>
+    <t>duty_station_city</t>
+  </si>
+  <si>
+    <t>The text description of the city of an employee’s official worksite.</t>
+  </si>
+  <si>
+    <t>BLOOMINGTON</t>
+  </si>
+  <si>
+    <t>department</t>
+  </si>
+  <si>
+    <t>Name of the department of the employee, aiding in the classification of roles within the organization.</t>
+  </si>
+  <si>
+    <t>department_code</t>
+  </si>
+  <si>
+    <t>Code representing the department to which the employee belongs, important for organizational structure.</t>
+  </si>
+  <si>
+    <t>pathways_group</t>
+  </si>
+  <si>
+    <t>Classification for employees within the pathways programs, which helps in the development of skills and experience.</t>
+  </si>
+  <si>
+    <t>AG</t>
+  </si>
+  <si>
+    <t>DEPARTMENT OF AGRICULTURE</t>
+  </si>
+  <si>
+    <t>RECENT GRAD</t>
+  </si>
+  <si>
+    <t>Employment</t>
+  </si>
+  <si>
+    <t>Accessions</t>
+  </si>
+  <si>
+    <t>Separations</t>
   </si>
 </sst>
 </file>
@@ -654,7 +690,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -670,6 +706,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1006,11 +1054,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D63578-2B10-4095-AE6C-A3776A8DE64E}">
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="69.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="86" style="1" customWidth="1"/>
     <col min="3" max="3" width="29.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" style="3" bestFit="1" customWidth="1"/>
@@ -1018,7 +1066,7 @@
     <col min="7" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1029,1340 +1077,1428 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>3</v>
+        <v>198</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>4</v>
+        <v>199</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>5</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C9" s="2">
         <v>35729.440000000002</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C10" s="4">
         <v>43540</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C12" s="2">
         <v>10</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C14" s="2">
         <v>1724</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C18" s="2">
         <v>148</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C20" s="2">
         <v>17020</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C21" s="2">
         <v>1</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="2">
-        <v>270675053</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>189</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>191</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C23" t="s">
+        <v>195</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>9</v>
+      <c r="A25" t="s">
+        <v>186</v>
+      </c>
+      <c r="B25" t="s">
+        <v>187</v>
+      </c>
+      <c r="C25" t="s">
+        <v>188</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>73</v>
+        <v>61</v>
+      </c>
+      <c r="C26" s="2">
+        <v>270675053</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" s="2">
-        <v>53</v>
+        <v>63</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C30" s="2">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C33" s="2">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>100</v>
+        <v>88</v>
+      </c>
+      <c r="C36" s="2">
+        <v>17</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C37" s="2">
-        <v>15.5</v>
+        <v>90</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>108</v>
+        <v>96</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>111</v>
+        <v>99</v>
+      </c>
+      <c r="C40" s="2">
+        <v>15.5</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C44" s="2">
-        <v>22</v>
+        <v>110</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C46" s="2">
-        <v>2210</v>
+        <v>116</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>130</v>
+        <v>119</v>
+      </c>
+      <c r="C47" s="2">
+        <v>22</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>123</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C49">
+        <v>2210</v>
+      </c>
+      <c r="D49" t="s">
+        <v>6</v>
+      </c>
+      <c r="E49" t="s">
+        <v>6</v>
+      </c>
+      <c r="F49" t="s">
+        <v>6</v>
+      </c>
+      <c r="G49"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>193</v>
+      </c>
+      <c r="B50" t="s">
+        <v>194</v>
+      </c>
+      <c r="C50" t="s">
+        <v>197</v>
+      </c>
+      <c r="D50" t="s">
+        <v>6</v>
+      </c>
+      <c r="E50" t="s">
+        <v>6</v>
+      </c>
+      <c r="F50" t="s">
+        <v>6</v>
+      </c>
+      <c r="G50"/>
+    </row>
+    <row r="51" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B53" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C53" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+      <c r="D53" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B54" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C54" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+      <c r="D54" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B55" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C55" s="2">
+        <v>202108</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
+      <c r="B56" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="C56" s="2">
+        <v>1559</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C51" s="2">
-        <v>202108</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="90" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+      <c r="B57" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="C57" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C52" s="2">
-        <v>1559</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+      <c r="D57" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B58" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C58" s="2">
+        <v>1</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
+      <c r="B59" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="C59" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C54" s="2">
-        <v>1</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+      <c r="F59" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B60" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F55" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+      <c r="F60" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B61" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C61" s="4">
+        <v>44073</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="F56" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+      <c r="B62" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="C62" s="2">
+        <v>202311</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C57" s="4">
-        <v>44073</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
+      <c r="B63" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C63" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C58" s="2">
-        <v>202311</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
+      <c r="D63" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B64" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C64" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+      <c r="D64" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B65" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C65" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
+      <c r="D65" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B66" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C66" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
+      <c r="D66" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B67" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C67" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="C64" s="2">
-        <v>2</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C66" s="2">
-        <v>1</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="D67" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C68" s="2">
+        <v>2</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C70" s="2">
+        <v>1</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B73" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C73" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>9</v>
+      <c r="D73" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A193">
-    <sortCondition ref="A2:A193"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A197">
+    <sortCondition ref="A2:A197"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="C62 C36" numberStoredAsText="1"/>
+    <ignoredError sqref="C66 C39" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{844ef997-7b63-48f0-882a-7dc8162e363b}" enabled="0" method="" siteId="{844ef997-7b63-48f0-882a-7dc8162e363b}" removed="1"/>
+</clbl:labelList>
 </file>